--- a/tables/table03.xlsx
+++ b/tables/table03.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\0228\科研数据会诊室 · 图书情报机构的核心能力重塑\manuscript\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wmj\Desktop\research-data-clinic\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963CCEB3-7CDE-4072-B245-3257B88E5B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91507182-D052-46B4-8677-AF920541EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>知识沉淀</t>
   </si>
   <si>
-    <t>形成课程案例、代码仓库、在线教材</t>
-  </si>
-  <si>
     <t>GitHub、bookdown、图书馆网页</t>
   </si>
   <si>
@@ -70,6 +67,10 @@
   </si>
   <si>
     <t>项目清单、合作记录、阶段性成果</t>
+  </si>
+  <si>
+    <t>课程案例、代码仓库、在线教材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -489,7 +490,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -503,10 +504,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -528,7 +529,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -536,10 +537,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
